--- a/output/yearly_total_coral_cover_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_89_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.261100513771321</v>
+        <v>1.251332124114066</v>
       </c>
       <c r="C3" t="n">
-        <v>4.660314027968488</v>
+        <v>4.648051999142445</v>
       </c>
       <c r="D3" t="n">
-        <v>6.072016378669259</v>
+        <v>6.19783716444553</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99343092040907</v>
+        <v>12.09722128770204</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.396741082338507</v>
+        <v>1.375065960292212</v>
       </c>
       <c r="C4" t="n">
-        <v>5.249065507100308</v>
+        <v>5.16464036021937</v>
       </c>
       <c r="D4" t="n">
-        <v>6.303355462045547</v>
+        <v>6.510727939297059</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94916205148436</v>
+        <v>13.05043425980864</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.575716266199622</v>
+        <v>1.542405308353319</v>
       </c>
       <c r="C5" t="n">
-        <v>6.086397047431218</v>
+        <v>5.834142251332025</v>
       </c>
       <c r="D5" t="n">
-        <v>6.582213548112995</v>
+        <v>6.845784850033521</v>
       </c>
       <c r="E5" t="n">
-        <v>14.24432686174383</v>
+        <v>14.22233240971886</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.786736825306561</v>
+        <v>1.732663157937146</v>
       </c>
       <c r="C6" t="n">
-        <v>7.141625138718191</v>
+        <v>6.657890742114886</v>
       </c>
       <c r="D6" t="n">
-        <v>6.909939223049916</v>
+        <v>7.323932661498878</v>
       </c>
       <c r="E6" t="n">
-        <v>15.83830118707467</v>
+        <v>15.71448656155091</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.020277163375222</v>
+        <v>1.940915969596575</v>
       </c>
       <c r="C7" t="n">
-        <v>8.385596922836209</v>
+        <v>7.632136377265639</v>
       </c>
       <c r="D7" t="n">
-        <v>7.307795272083133</v>
+        <v>7.745796562225709</v>
       </c>
       <c r="E7" t="n">
-        <v>17.71366935829456</v>
+        <v>17.31884890908792</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.233841928487122</v>
+        <v>1.160155027691339</v>
       </c>
       <c r="C8" t="n">
-        <v>6.070803840816099</v>
+        <v>5.268015911447763</v>
       </c>
       <c r="D8" t="n">
-        <v>5.468649527384977</v>
+        <v>5.957328645198244</v>
       </c>
       <c r="E8" t="n">
-        <v>12.7732952966882</v>
+        <v>12.38549958433735</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.521494017317107</v>
+        <v>1.443463578301486</v>
       </c>
       <c r="C9" t="n">
-        <v>7.55090870978495</v>
+        <v>6.462209943357163</v>
       </c>
       <c r="D9" t="n">
-        <v>5.884706981044223</v>
+        <v>6.463991274062011</v>
       </c>
       <c r="E9" t="n">
-        <v>14.95710970814628</v>
+        <v>14.36966479572066</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.810800995904625</v>
+        <v>1.747351146746554</v>
       </c>
       <c r="C10" t="n">
-        <v>9.1988124499318</v>
+        <v>7.820176827803135</v>
       </c>
       <c r="D10" t="n">
-        <v>6.282878172262216</v>
+        <v>6.993414833503429</v>
       </c>
       <c r="E10" t="n">
-        <v>17.29249161809864</v>
+        <v>16.56094280805312</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.093161861700636</v>
+        <v>2.0652725216769</v>
       </c>
       <c r="C11" t="n">
-        <v>10.95344933114425</v>
+        <v>9.312209992401872</v>
       </c>
       <c r="D11" t="n">
-        <v>6.755707511140715</v>
+        <v>7.610556619390499</v>
       </c>
       <c r="E11" t="n">
-        <v>19.8023187039856</v>
+        <v>18.98803913346927</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.371058870944251</v>
+        <v>2.378724294324483</v>
       </c>
       <c r="C12" t="n">
-        <v>12.77904485142971</v>
+        <v>10.93230224516082</v>
       </c>
       <c r="D12" t="n">
-        <v>7.123887356515199</v>
+        <v>8.204808934381346</v>
       </c>
       <c r="E12" t="n">
-        <v>22.27399107888916</v>
+        <v>21.51583547386665</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.631125806792929</v>
+        <v>2.674035292324699</v>
       </c>
       <c r="C13" t="n">
-        <v>14.63501314910262</v>
+        <v>12.6451936771219</v>
       </c>
       <c r="D13" t="n">
-        <v>7.581915708944958</v>
+        <v>8.710239870898269</v>
       </c>
       <c r="E13" t="n">
-        <v>24.84805466484051</v>
+        <v>24.02946884034487</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.518950230533623</v>
+        <v>1.537230372786698</v>
       </c>
       <c r="C14" t="n">
-        <v>10.2185602495611</v>
+        <v>8.950466192416618</v>
       </c>
       <c r="D14" t="n">
-        <v>5.762809936543565</v>
+        <v>6.574126239333129</v>
       </c>
       <c r="E14" t="n">
-        <v>17.50032041663828</v>
+        <v>17.06182280453644</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.526912204415064</v>
+        <v>1.564984380385755</v>
       </c>
       <c r="C15" t="n">
-        <v>11.06823343515558</v>
+        <v>9.804341258185282</v>
       </c>
       <c r="D15" t="n">
-        <v>5.723697108006372</v>
+        <v>6.61072579374745</v>
       </c>
       <c r="E15" t="n">
-        <v>18.31884274757702</v>
+        <v>17.98005143231849</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.738361024955742</v>
+        <v>1.801988093667978</v>
       </c>
       <c r="C16" t="n">
-        <v>13.07821459744529</v>
+        <v>11.6853993119533</v>
       </c>
       <c r="D16" t="n">
-        <v>6.107796079815894</v>
+        <v>7.102051249814807</v>
       </c>
       <c r="E16" t="n">
-        <v>20.92437170221693</v>
+        <v>20.58943865543608</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.371344463200114</v>
+        <v>1.436993932183099</v>
       </c>
       <c r="C17" t="n">
-        <v>11.99233291420902</v>
+        <v>10.84837103678951</v>
       </c>
       <c r="D17" t="n">
-        <v>5.626700434826787</v>
+        <v>6.610352729619837</v>
       </c>
       <c r="E17" t="n">
-        <v>18.99037781223592</v>
+        <v>18.89571769859245</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.5335782713269</v>
+        <v>1.619117948797925</v>
       </c>
       <c r="C18" t="n">
-        <v>14.01280895945713</v>
+        <v>12.72605187845492</v>
       </c>
       <c r="D18" t="n">
-        <v>5.95666583822414</v>
+        <v>7.082543922931425</v>
       </c>
       <c r="E18" t="n">
-        <v>21.50305306900817</v>
+        <v>21.42771375018426</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.510919534312884</v>
+        <v>1.604195383693373</v>
       </c>
       <c r="C19" t="n">
-        <v>14.99458611613506</v>
+        <v>13.6682155152665</v>
       </c>
       <c r="D19" t="n">
-        <v>5.997751979646869</v>
+        <v>7.179442421340586</v>
       </c>
       <c r="E19" t="n">
-        <v>22.50325763009482</v>
+        <v>22.45185332030045</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.656581441191983</v>
+        <v>1.771534279882242</v>
       </c>
       <c r="C20" t="n">
-        <v>17.28619142486501</v>
+        <v>15.66252798419642</v>
       </c>
       <c r="D20" t="n">
-        <v>6.298824548108238</v>
+        <v>7.641207454033072</v>
       </c>
       <c r="E20" t="n">
-        <v>25.24159741416523</v>
+        <v>25.07526971811174</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9716160679389834</v>
+        <v>1.04503116126256</v>
       </c>
       <c r="C21" t="n">
-        <v>12.75850845755732</v>
+        <v>11.46160992277024</v>
       </c>
       <c r="D21" t="n">
-        <v>5.216094275002601</v>
+        <v>6.37599973513908</v>
       </c>
       <c r="E21" t="n">
-        <v>18.9462188004989</v>
+        <v>18.88264081917188</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_89_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251332124114066</v>
+        <v>1.259205740702125</v>
       </c>
       <c r="C3" t="n">
-        <v>4.648051999142445</v>
+        <v>4.658262175266612</v>
       </c>
       <c r="D3" t="n">
-        <v>6.19783716444553</v>
+        <v>6.114800943620335</v>
       </c>
       <c r="E3" t="n">
-        <v>12.09722128770204</v>
+        <v>12.03226885958907</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.375065960292212</v>
+        <v>1.388045957338757</v>
       </c>
       <c r="C4" t="n">
-        <v>5.16464036021937</v>
+        <v>5.193159389620582</v>
       </c>
       <c r="D4" t="n">
-        <v>6.510727939297059</v>
+        <v>6.335742535536042</v>
       </c>
       <c r="E4" t="n">
-        <v>13.05043425980864</v>
+        <v>12.91694788249538</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.542405308353319</v>
+        <v>1.570442765847347</v>
       </c>
       <c r="C5" t="n">
-        <v>5.834142251332025</v>
+        <v>5.922299283031313</v>
       </c>
       <c r="D5" t="n">
-        <v>6.845784850033521</v>
+        <v>6.628777522740059</v>
       </c>
       <c r="E5" t="n">
-        <v>14.22233240971886</v>
+        <v>14.12151957161872</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.732663157937146</v>
+        <v>1.786827946875702</v>
       </c>
       <c r="C6" t="n">
-        <v>6.657890742114886</v>
+        <v>6.858566831253203</v>
       </c>
       <c r="D6" t="n">
-        <v>7.323932661498878</v>
+        <v>6.930424079967965</v>
       </c>
       <c r="E6" t="n">
-        <v>15.71448656155091</v>
+        <v>15.57581885809687</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.940915969596575</v>
+        <v>2.025596159119817</v>
       </c>
       <c r="C7" t="n">
-        <v>7.632136377265639</v>
+        <v>8.014867493502537</v>
       </c>
       <c r="D7" t="n">
-        <v>7.745796562225709</v>
+        <v>7.23209855932255</v>
       </c>
       <c r="E7" t="n">
-        <v>17.31884890908792</v>
+        <v>17.2725622119449</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.160155027691339</v>
+        <v>1.255109848065856</v>
       </c>
       <c r="C8" t="n">
-        <v>5.268015911447763</v>
+        <v>5.803840792395416</v>
       </c>
       <c r="D8" t="n">
-        <v>5.957328645198244</v>
+        <v>5.473891645946862</v>
       </c>
       <c r="E8" t="n">
-        <v>12.38549958433735</v>
+        <v>12.53284228640814</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.443463578301486</v>
+        <v>1.569124998870851</v>
       </c>
       <c r="C9" t="n">
-        <v>6.462209943357163</v>
+        <v>7.298538326957049</v>
       </c>
       <c r="D9" t="n">
-        <v>6.463991274062011</v>
+        <v>5.886204037870226</v>
       </c>
       <c r="E9" t="n">
-        <v>14.36966479572066</v>
+        <v>14.75386736369813</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.747351146746554</v>
+        <v>1.887962043842759</v>
       </c>
       <c r="C10" t="n">
-        <v>7.820176827803135</v>
+        <v>8.979164050900387</v>
       </c>
       <c r="D10" t="n">
-        <v>6.993414833503429</v>
+        <v>6.278069963020852</v>
       </c>
       <c r="E10" t="n">
-        <v>16.56094280805312</v>
+        <v>17.145196057764</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.0652725216769</v>
+        <v>2.204638669758069</v>
       </c>
       <c r="C11" t="n">
-        <v>9.312209992401872</v>
+        <v>10.75043082653408</v>
       </c>
       <c r="D11" t="n">
-        <v>7.610556619390499</v>
+        <v>6.728227749139054</v>
       </c>
       <c r="E11" t="n">
-        <v>18.98803913346927</v>
+        <v>19.6832972454312</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.378724294324483</v>
+        <v>2.510005890620202</v>
       </c>
       <c r="C12" t="n">
-        <v>10.93230224516082</v>
+        <v>12.5836743611954</v>
       </c>
       <c r="D12" t="n">
-        <v>8.204808934381346</v>
+        <v>7.194648349964054</v>
       </c>
       <c r="E12" t="n">
-        <v>21.51583547386665</v>
+        <v>22.28832860177966</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.674035292324699</v>
+        <v>2.788834619148705</v>
       </c>
       <c r="C13" t="n">
-        <v>12.6451936771219</v>
+        <v>14.40536944285186</v>
       </c>
       <c r="D13" t="n">
-        <v>8.710239870898269</v>
+        <v>7.561027648599808</v>
       </c>
       <c r="E13" t="n">
-        <v>24.02946884034487</v>
+        <v>24.75523171060037</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.537230372786698</v>
+        <v>1.603301993282509</v>
       </c>
       <c r="C14" t="n">
-        <v>8.950466192416618</v>
+        <v>9.949924625248039</v>
       </c>
       <c r="D14" t="n">
-        <v>6.574126239333129</v>
+        <v>5.754072381975768</v>
       </c>
       <c r="E14" t="n">
-        <v>17.06182280453644</v>
+        <v>17.30729900050632</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.564984380385755</v>
+        <v>1.618028208846211</v>
       </c>
       <c r="C15" t="n">
-        <v>9.804341258185282</v>
+        <v>10.78815063261101</v>
       </c>
       <c r="D15" t="n">
-        <v>6.61072579374745</v>
+        <v>5.705240251166532</v>
       </c>
       <c r="E15" t="n">
-        <v>17.98005143231849</v>
+        <v>18.11141909262375</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.801988093667978</v>
+        <v>1.844713753756799</v>
       </c>
       <c r="C16" t="n">
-        <v>11.6853993119533</v>
+        <v>12.70791899835748</v>
       </c>
       <c r="D16" t="n">
-        <v>7.102051249814807</v>
+        <v>6.099598486485434</v>
       </c>
       <c r="E16" t="n">
-        <v>20.58943865543608</v>
+        <v>20.65223123859971</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.436993932183099</v>
+        <v>1.458248769980042</v>
       </c>
       <c r="C17" t="n">
-        <v>10.84837103678951</v>
+        <v>11.62030943916174</v>
       </c>
       <c r="D17" t="n">
-        <v>6.610352729619837</v>
+        <v>5.620535059244117</v>
       </c>
       <c r="E17" t="n">
-        <v>18.89571769859245</v>
+        <v>18.69909326838589</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.619117948797925</v>
+        <v>1.653400578630223</v>
       </c>
       <c r="C18" t="n">
-        <v>12.72605187845492</v>
+        <v>13.51584827156739</v>
       </c>
       <c r="D18" t="n">
-        <v>7.082543922931425</v>
+        <v>5.951923996812629</v>
       </c>
       <c r="E18" t="n">
-        <v>21.42771375018426</v>
+        <v>21.12117284701024</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.604195383693373</v>
+        <v>1.647303925386851</v>
       </c>
       <c r="C19" t="n">
-        <v>13.6682155152665</v>
+        <v>14.41116290793231</v>
       </c>
       <c r="D19" t="n">
-        <v>7.179442421340586</v>
+        <v>5.984586742932919</v>
       </c>
       <c r="E19" t="n">
-        <v>22.45185332030045</v>
+        <v>22.04305357625208</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.771534279882242</v>
+        <v>1.821269618579386</v>
       </c>
       <c r="C20" t="n">
-        <v>15.66252798419642</v>
+        <v>16.52490498508386</v>
       </c>
       <c r="D20" t="n">
-        <v>7.641207454033072</v>
+        <v>6.373201754181977</v>
       </c>
       <c r="E20" t="n">
-        <v>25.07526971811174</v>
+        <v>24.71937635784523</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.04503116126256</v>
+        <v>1.077026318943964</v>
       </c>
       <c r="C21" t="n">
-        <v>11.46160992277024</v>
+        <v>12.07296385315881</v>
       </c>
       <c r="D21" t="n">
-        <v>6.37599973513908</v>
+        <v>5.289028311951097</v>
       </c>
       <c r="E21" t="n">
-        <v>18.88264081917188</v>
+        <v>18.43901848405387</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_89_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_89_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.259205740702125</v>
+        <v>2.601945097402936</v>
       </c>
       <c r="C3" t="n">
-        <v>4.658262175266612</v>
+        <v>7.683900831047272</v>
       </c>
       <c r="D3" t="n">
-        <v>6.114800943620335</v>
+        <v>8.130675211996826</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03226885958907</v>
+        <v>18.41652114044703</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.388045957338757</v>
+        <v>1.108304008888495</v>
       </c>
       <c r="C4" t="n">
-        <v>5.193159389620582</v>
+        <v>4.423065175787865</v>
       </c>
       <c r="D4" t="n">
-        <v>6.335742535536042</v>
+        <v>5.710110321483881</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91694788249538</v>
+        <v>11.24147950616024</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.570442765847347</v>
+        <v>1.243916058497486</v>
       </c>
       <c r="C5" t="n">
-        <v>5.922299283031313</v>
+        <v>4.987933182831799</v>
       </c>
       <c r="D5" t="n">
-        <v>6.628777522740059</v>
+        <v>5.943407912146271</v>
       </c>
       <c r="E5" t="n">
-        <v>14.12151957161872</v>
+        <v>12.17525715347556</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.786827946875702</v>
+        <v>1.402051111810368</v>
       </c>
       <c r="C6" t="n">
-        <v>6.858566831253203</v>
+        <v>5.697859622262879</v>
       </c>
       <c r="D6" t="n">
-        <v>6.930424079967965</v>
+        <v>6.249162437225815</v>
       </c>
       <c r="E6" t="n">
-        <v>15.57581885809687</v>
+        <v>13.34907317129906</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.025596159119817</v>
+        <v>1.573932952916109</v>
       </c>
       <c r="C7" t="n">
-        <v>8.014867493502537</v>
+        <v>6.609140164545922</v>
       </c>
       <c r="D7" t="n">
-        <v>7.23209855932255</v>
+        <v>6.605882665142476</v>
       </c>
       <c r="E7" t="n">
-        <v>17.2725622119449</v>
+        <v>14.78895578260451</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.255109848065856</v>
+        <v>1.74747352600657</v>
       </c>
       <c r="C8" t="n">
-        <v>5.803840792395416</v>
+        <v>7.651974036048919</v>
       </c>
       <c r="D8" t="n">
-        <v>5.473891645946862</v>
+        <v>6.919495734798968</v>
       </c>
       <c r="E8" t="n">
-        <v>12.53284228640814</v>
+        <v>16.31894329685446</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.569124998870851</v>
+        <v>1.928094656768401</v>
       </c>
       <c r="C9" t="n">
-        <v>7.298538326957049</v>
+        <v>8.860757271190403</v>
       </c>
       <c r="D9" t="n">
-        <v>5.886204037870226</v>
+        <v>7.270286647262245</v>
       </c>
       <c r="E9" t="n">
-        <v>14.75386736369813</v>
+        <v>18.05913857522105</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.887962043842759</v>
+        <v>1.178254324728852</v>
       </c>
       <c r="C10" t="n">
-        <v>8.979164050900387</v>
+        <v>6.618540505473255</v>
       </c>
       <c r="D10" t="n">
-        <v>6.278069963020852</v>
+        <v>5.726230017083328</v>
       </c>
       <c r="E10" t="n">
-        <v>17.145196057764</v>
+        <v>13.52302484728543</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.204638669758069</v>
+        <v>1.135332315099181</v>
       </c>
       <c r="C11" t="n">
-        <v>10.75043082653408</v>
+        <v>7.035282588448983</v>
       </c>
       <c r="D11" t="n">
-        <v>6.728227749139054</v>
+        <v>5.55105677421457</v>
       </c>
       <c r="E11" t="n">
-        <v>19.6832972454312</v>
+        <v>13.72167167776274</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.510005890620202</v>
+        <v>1.248036951546715</v>
       </c>
       <c r="C12" t="n">
-        <v>12.5836743611954</v>
+        <v>8.333457395251584</v>
       </c>
       <c r="D12" t="n">
-        <v>7.194648349964054</v>
+        <v>5.893529643364027</v>
       </c>
       <c r="E12" t="n">
-        <v>22.28832860177966</v>
+        <v>15.47502399016233</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.788834619148705</v>
+        <v>0.9944809719708916</v>
       </c>
       <c r="C13" t="n">
-        <v>14.40536944285186</v>
+        <v>7.963574130199556</v>
       </c>
       <c r="D13" t="n">
-        <v>7.561027648599808</v>
+        <v>5.336387821203963</v>
       </c>
       <c r="E13" t="n">
-        <v>24.75523171060037</v>
+        <v>14.29444292337441</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.603301993282509</v>
+        <v>1.091693629645411</v>
       </c>
       <c r="C14" t="n">
-        <v>9.949924625248039</v>
+        <v>9.364616461453135</v>
       </c>
       <c r="D14" t="n">
-        <v>5.754072381975768</v>
+        <v>5.677044457100563</v>
       </c>
       <c r="E14" t="n">
-        <v>17.30729900050632</v>
+        <v>16.13335454819911</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.618028208846211</v>
+        <v>1.067601540983194</v>
       </c>
       <c r="C15" t="n">
-        <v>10.78815063261101</v>
+        <v>10.15491354589478</v>
       </c>
       <c r="D15" t="n">
-        <v>5.705240251166532</v>
+        <v>5.702707342089576</v>
       </c>
       <c r="E15" t="n">
-        <v>18.11141909262375</v>
+        <v>16.92522242896754</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.844713753756799</v>
+        <v>1.176074844825424</v>
       </c>
       <c r="C16" t="n">
-        <v>12.70791899835748</v>
+        <v>11.90120709230083</v>
       </c>
       <c r="D16" t="n">
-        <v>6.099598486485434</v>
+        <v>6.081907392854905</v>
       </c>
       <c r="E16" t="n">
-        <v>20.65223123859971</v>
+        <v>19.15918932998116</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.458248769980042</v>
+        <v>0.7067110849020666</v>
       </c>
       <c r="C17" t="n">
-        <v>11.62030943916174</v>
+        <v>8.949916413702239</v>
       </c>
       <c r="D17" t="n">
-        <v>5.620535059244117</v>
+        <v>5.03936005328409</v>
       </c>
       <c r="E17" t="n">
-        <v>18.69909326838589</v>
+        <v>14.6959875518884</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.653400578630223</v>
+        <v>0.5570534648666827</v>
       </c>
       <c r="C18" t="n">
-        <v>13.51584827156739</v>
+        <v>7.975306015265303</v>
       </c>
       <c r="D18" t="n">
-        <v>5.951923996812629</v>
+        <v>4.549958822717055</v>
       </c>
       <c r="E18" t="n">
-        <v>21.12117284701024</v>
+        <v>13.08231830284904</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.647303925386851</v>
+        <v>0.6549042585489623</v>
       </c>
       <c r="C19" t="n">
-        <v>14.41116290793231</v>
+        <v>9.893955188628931</v>
       </c>
       <c r="D19" t="n">
-        <v>5.984586742932919</v>
+        <v>4.99122496334487</v>
       </c>
       <c r="E19" t="n">
-        <v>22.04305357625208</v>
+        <v>15.54008441052276</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.821269618579386</v>
+        <v>0.7454312143575607</v>
       </c>
       <c r="C20" t="n">
-        <v>16.52490498508386</v>
+        <v>11.93844478272291</v>
       </c>
       <c r="D20" t="n">
-        <v>6.373201754181977</v>
+        <v>5.466950448391746</v>
       </c>
       <c r="E20" t="n">
-        <v>24.71937635784523</v>
+        <v>18.15082644547222</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.077026318943964</v>
+        <v>0.8257676289960771</v>
       </c>
       <c r="C21" t="n">
-        <v>12.07296385315881</v>
+        <v>14.07401111133987</v>
       </c>
       <c r="D21" t="n">
-        <v>5.289028311951097</v>
+        <v>5.929854308421159</v>
       </c>
       <c r="E21" t="n">
-        <v>18.43901848405387</v>
+        <v>20.82963304875711</v>
       </c>
     </row>
   </sheetData>
